--- a/tams-valuation-parent/tams-valuation/src/main/resources/tpl/basedata/marketdata/fundmarketinfo/Valfundmarketinfo001.xlsx
+++ b/tams-valuation-parent/tams-valuation/src/main/resources/tpl/basedata/marketdata/fundmarketinfo/Valfundmarketinfo001.xlsx
@@ -4,13 +4,12 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2715" windowWidth="13335" windowHeight="6135"/>
+    <workbookView xWindow="0" yWindow="2712" windowWidth="13332" windowHeight="6132"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
-  <oleSize ref="A1"/>
 </workbook>
 </file>
 
@@ -365,13 +364,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:J1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="3" width="15.5" customWidth="1"/>
+    <col min="2" max="3" width="15.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
